--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260716.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260716.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>378,825,000</t>
+          <t>31,686,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>31,686,000</t>
+          <t>378,825,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>188,806,000</t>
+          <t>273,866,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>273,866,000</t>
+          <t>188,806,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
